--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>120300</v>
+        <v>151800</v>
       </c>
       <c r="E8" s="3">
-        <v>110300</v>
+        <v>130300</v>
       </c>
       <c r="F8" s="3">
-        <v>126300</v>
+        <v>129100</v>
       </c>
       <c r="G8" s="3">
-        <v>117200</v>
+        <v>133200</v>
       </c>
       <c r="H8" s="3">
-        <v>89600</v>
+        <v>139100</v>
       </c>
       <c r="I8" s="3">
-        <v>90900</v>
+        <v>147600</v>
       </c>
       <c r="J8" s="3">
+        <v>141600</v>
+      </c>
+      <c r="K8" s="3">
         <v>96700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>83200</v>
+        <v>99100</v>
       </c>
       <c r="E9" s="3">
-        <v>78400</v>
+        <v>84300</v>
       </c>
       <c r="F9" s="3">
-        <v>91700</v>
+        <v>81600</v>
       </c>
       <c r="G9" s="3">
-        <v>85600</v>
+        <v>84700</v>
       </c>
       <c r="H9" s="3">
+        <v>89200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>96700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>93100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>66600</v>
+      </c>
+      <c r="L9" s="3">
         <v>65700</v>
       </c>
-      <c r="I9" s="3">
-        <v>65500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>66600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>65700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>37100</v>
+        <v>52700</v>
       </c>
       <c r="E10" s="3">
-        <v>31900</v>
+        <v>46000</v>
       </c>
       <c r="F10" s="3">
-        <v>34600</v>
+        <v>47500</v>
       </c>
       <c r="G10" s="3">
-        <v>31600</v>
+        <v>48500</v>
       </c>
       <c r="H10" s="3">
-        <v>23900</v>
+        <v>49900</v>
       </c>
       <c r="I10" s="3">
-        <v>25400</v>
+        <v>51000</v>
       </c>
       <c r="J10" s="3">
+        <v>48500</v>
+      </c>
+      <c r="K10" s="3">
         <v>30100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,37 +822,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -867,66 +884,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1700</v>
+        <v>-72500</v>
       </c>
       <c r="E14" s="3">
-        <v>19000</v>
+        <v>7600</v>
       </c>
       <c r="F14" s="3">
-        <v>-200</v>
+        <v>4000</v>
       </c>
       <c r="G14" s="3">
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="H14" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="I14" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="J14" s="3">
+        <v>400</v>
+      </c>
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>125000</v>
+        <v>144900</v>
       </c>
       <c r="E17" s="3">
-        <v>129100</v>
+        <v>109600</v>
       </c>
       <c r="F17" s="3">
-        <v>121800</v>
+        <v>107500</v>
       </c>
       <c r="G17" s="3">
-        <v>123300</v>
+        <v>108800</v>
       </c>
       <c r="H17" s="3">
-        <v>86000</v>
+        <v>114200</v>
       </c>
       <c r="I17" s="3">
-        <v>87700</v>
+        <v>119400</v>
       </c>
       <c r="J17" s="3">
+        <v>116200</v>
+      </c>
+      <c r="K17" s="3">
         <v>99200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-4700</v>
+        <v>6900</v>
       </c>
       <c r="E18" s="3">
-        <v>-18800</v>
+        <v>20700</v>
       </c>
       <c r="F18" s="3">
-        <v>4500</v>
+        <v>21600</v>
       </c>
       <c r="G18" s="3">
-        <v>-6100</v>
+        <v>24400</v>
       </c>
       <c r="H18" s="3">
-        <v>3600</v>
+        <v>24900</v>
       </c>
       <c r="I18" s="3">
-        <v>3200</v>
+        <v>28300</v>
       </c>
       <c r="J18" s="3">
+        <v>25400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1006,153 +1039,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>-1300</v>
       </c>
       <c r="E20" s="3">
-        <v>2200</v>
+        <v>-1400</v>
       </c>
       <c r="F20" s="3">
-        <v>1200</v>
+        <v>-700</v>
       </c>
       <c r="G20" s="3">
-        <v>2400</v>
+        <v>-1500</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>-800</v>
       </c>
       <c r="I20" s="3">
-        <v>2800</v>
+        <v>-1600</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>3300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5400</v>
+        <v>16000</v>
       </c>
       <c r="E21" s="3">
-        <v>-8200</v>
+        <v>28700</v>
       </c>
       <c r="F21" s="3">
-        <v>14200</v>
+        <v>28000</v>
       </c>
       <c r="G21" s="3">
-        <v>4100</v>
+        <v>32000</v>
       </c>
       <c r="H21" s="3">
-        <v>12700</v>
+        <v>31500</v>
       </c>
       <c r="I21" s="3">
-        <v>12900</v>
+        <v>35300</v>
       </c>
       <c r="J21" s="3">
+        <v>31200</v>
+      </c>
+      <c r="K21" s="3">
         <v>7900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>17</v>
+      <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
+        <v>800</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2600</v>
+        <v>80000</v>
       </c>
       <c r="E23" s="3">
-        <v>-16600</v>
+        <v>13900</v>
       </c>
       <c r="F23" s="3">
-        <v>5700</v>
+        <v>17700</v>
       </c>
       <c r="G23" s="3">
-        <v>-3800</v>
+        <v>23500</v>
       </c>
       <c r="H23" s="3">
-        <v>5600</v>
+        <v>23200</v>
       </c>
       <c r="I23" s="3">
-        <v>5900</v>
+        <v>27300</v>
       </c>
       <c r="J23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-800</v>
+        <v>-2600</v>
       </c>
       <c r="E24" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="F24" s="3">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="G24" s="3">
-        <v>3300</v>
+        <v>5000</v>
       </c>
       <c r="H24" s="3">
-        <v>2100</v>
+        <v>7900</v>
       </c>
       <c r="I24" s="3">
-        <v>3600</v>
+        <v>6700</v>
       </c>
       <c r="J24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1800</v>
+        <v>82600</v>
       </c>
       <c r="E26" s="3">
-        <v>-20000</v>
+        <v>9500</v>
       </c>
       <c r="F26" s="3">
-        <v>1800</v>
+        <v>13000</v>
       </c>
       <c r="G26" s="3">
-        <v>-7000</v>
+        <v>18400</v>
       </c>
       <c r="H26" s="3">
-        <v>3500</v>
+        <v>15400</v>
       </c>
       <c r="I26" s="3">
-        <v>2300</v>
+        <v>20600</v>
       </c>
       <c r="J26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1800</v>
+        <v>82600</v>
       </c>
       <c r="E27" s="3">
-        <v>-20000</v>
+        <v>9500</v>
       </c>
       <c r="F27" s="3">
-        <v>1800</v>
+        <v>13000</v>
       </c>
       <c r="G27" s="3">
-        <v>-7000</v>
+        <v>18400</v>
       </c>
       <c r="H27" s="3">
-        <v>3500</v>
+        <v>15400</v>
       </c>
       <c r="I27" s="3">
-        <v>2300</v>
+        <v>20600</v>
       </c>
       <c r="J27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2100</v>
+        <v>1300</v>
       </c>
       <c r="E32" s="3">
-        <v>-2200</v>
+        <v>1400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1200</v>
+        <v>700</v>
       </c>
       <c r="G32" s="3">
-        <v>-2400</v>
+        <v>1500</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>800</v>
       </c>
       <c r="I32" s="3">
-        <v>-2800</v>
+        <v>1600</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1800</v>
+        <v>82600</v>
       </c>
       <c r="E33" s="3">
-        <v>-20000</v>
+        <v>9500</v>
       </c>
       <c r="F33" s="3">
-        <v>1800</v>
+        <v>13000</v>
       </c>
       <c r="G33" s="3">
-        <v>-7000</v>
+        <v>18400</v>
       </c>
       <c r="H33" s="3">
-        <v>3500</v>
+        <v>15400</v>
       </c>
       <c r="I33" s="3">
-        <v>2300</v>
+        <v>20600</v>
       </c>
       <c r="J33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1800</v>
+        <v>82600</v>
       </c>
       <c r="E35" s="3">
-        <v>-20000</v>
+        <v>9500</v>
       </c>
       <c r="F35" s="3">
-        <v>1800</v>
+        <v>13000</v>
       </c>
       <c r="G35" s="3">
-        <v>-7000</v>
+        <v>18400</v>
       </c>
       <c r="H35" s="3">
-        <v>3500</v>
+        <v>15400</v>
       </c>
       <c r="I35" s="3">
-        <v>2300</v>
+        <v>20600</v>
       </c>
       <c r="J35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,269 +1616,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>185600</v>
+        <v>99900</v>
       </c>
       <c r="E41" s="3">
-        <v>198200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>187300</v>
+        <v>10400</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G41" s="3">
-        <v>181100</v>
+        <v>7400</v>
       </c>
       <c r="H41" s="3">
-        <v>236500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>235300</v>
-      </c>
-      <c r="J41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="3">
         <v>264800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="E42" s="3">
-        <v>4000</v>
+        <v>8400</v>
       </c>
       <c r="F42" s="3">
-        <v>25900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="H42" s="3">
-        <v>18800</v>
+        <v>9000</v>
       </c>
       <c r="I42" s="3">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>32200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>287200</v>
+        <v>250600</v>
       </c>
       <c r="E43" s="3">
-        <v>276700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>284000</v>
+        <v>123900</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G43" s="3">
-        <v>287600</v>
+        <v>122100</v>
       </c>
       <c r="H43" s="3">
-        <v>274600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>282500</v>
-      </c>
-      <c r="J43" s="3">
+        <v>131700</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="3">
         <v>235300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>204700</v>
+        <v>297500</v>
       </c>
       <c r="E44" s="3">
-        <v>209200</v>
-      </c>
-      <c r="F44" s="3">
-        <v>194600</v>
+        <v>146700</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G44" s="3">
-        <v>183300</v>
+        <v>141200</v>
       </c>
       <c r="H44" s="3">
-        <v>164500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>152800</v>
-      </c>
-      <c r="J44" s="3">
+        <v>140200</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="3">
         <v>70100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>30000</v>
+        <v>5800</v>
       </c>
       <c r="E45" s="3">
-        <v>27000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>27900</v>
+        <v>3900</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G45" s="3">
-        <v>48200</v>
+        <v>5000</v>
       </c>
       <c r="H45" s="3">
-        <v>60700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>62600</v>
-      </c>
-      <c r="J45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="3">
         <v>71700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>707600</v>
+        <v>677300</v>
       </c>
       <c r="E46" s="3">
-        <v>715100</v>
-      </c>
-      <c r="F46" s="3">
-        <v>719700</v>
+        <v>295000</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G46" s="3">
-        <v>709000</v>
+        <v>288300</v>
       </c>
       <c r="H46" s="3">
-        <v>755200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>752100</v>
-      </c>
-      <c r="J46" s="3">
+        <v>295700</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="3">
         <v>750000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+        <v>19600</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>19400</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>227900</v>
+        <v>229600</v>
       </c>
       <c r="E48" s="3">
-        <v>231600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>234000</v>
+        <v>78000</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G48" s="3">
-        <v>228000</v>
+        <v>85100</v>
       </c>
       <c r="H48" s="3">
-        <v>191800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>189600</v>
-      </c>
-      <c r="J48" s="3">
+        <v>84500</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="3">
         <v>186100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>55000</v>
+        <v>59700</v>
       </c>
       <c r="E49" s="3">
-        <v>56500</v>
+        <v>61700</v>
       </c>
       <c r="F49" s="3">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>58700</v>
+        <v>65700</v>
       </c>
       <c r="H49" s="3">
-        <v>22100</v>
+        <v>67700</v>
       </c>
       <c r="I49" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>23300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17700</v>
+        <v>7700</v>
       </c>
       <c r="E52" s="3">
-        <v>17700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>15900</v>
+        <v>2200</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G52" s="3">
-        <v>11700</v>
+        <v>2100</v>
       </c>
       <c r="H52" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="3">
         <v>10400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1008200</v>
+        <v>1132800</v>
       </c>
       <c r="E54" s="3">
-        <v>1021000</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1028200</v>
+        <v>471600</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G54" s="3">
-        <v>1007600</v>
+        <v>475300</v>
       </c>
       <c r="H54" s="3">
-        <v>979700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>975400</v>
-      </c>
-      <c r="J54" s="3">
+        <v>487000</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="3">
         <v>970000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,54 +2092,58 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>60800</v>
+        <v>83600</v>
       </c>
       <c r="E57" s="3">
-        <v>62900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>65700</v>
+        <v>36700</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G57" s="3">
-        <v>50500</v>
+        <v>32000</v>
       </c>
       <c r="H57" s="3">
-        <v>54400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>47200</v>
-      </c>
-      <c r="J57" s="3">
+        <v>39700</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="3">
         <v>43000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>28100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2020,83 +2154,92 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>65600</v>
+        <v>15500</v>
       </c>
       <c r="E59" s="3">
-        <v>70600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>52000</v>
+        <v>6600</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G59" s="3">
-        <v>56300</v>
+        <v>2700</v>
       </c>
       <c r="H59" s="3">
-        <v>33700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>36100</v>
-      </c>
-      <c r="J59" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="3">
         <v>52600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>126400</v>
+        <v>174800</v>
       </c>
       <c r="E60" s="3">
-        <v>133600</v>
-      </c>
-      <c r="F60" s="3">
-        <v>117700</v>
+        <v>80700</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G60" s="3">
-        <v>106700</v>
+        <v>78600</v>
       </c>
       <c r="H60" s="3">
-        <v>88100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>83400</v>
-      </c>
-      <c r="J60" s="3">
+        <v>103100</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="3">
         <v>87600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>51700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>38400</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>67700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2107,37 +2250,43 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29200</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>30100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>29200</v>
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G62" s="3">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="3">
         <v>10000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>155600</v>
+        <v>228400</v>
       </c>
       <c r="E66" s="3">
-        <v>163700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>146900</v>
+        <v>119100</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G66" s="3">
-        <v>137100</v>
+        <v>146400</v>
       </c>
       <c r="H66" s="3">
-        <v>100300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>95000</v>
-      </c>
-      <c r="J66" s="3">
+        <v>179000</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="3">
         <v>97600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>929000</v>
+        <v>179500</v>
       </c>
       <c r="E72" s="3">
-        <v>930800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>950700</v>
+        <v>171900</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G72" s="3">
-        <v>948900</v>
+        <v>145900</v>
       </c>
       <c r="H72" s="3">
-        <v>956000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>955000</v>
-      </c>
-      <c r="J72" s="3">
+        <v>127500</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="3">
         <v>950200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>852500</v>
+        <v>904400</v>
       </c>
       <c r="E76" s="3">
-        <v>857400</v>
+        <v>352500</v>
       </c>
       <c r="F76" s="3">
-        <v>881300</v>
+        <v>328900</v>
       </c>
       <c r="G76" s="3">
-        <v>870500</v>
+        <v>328900</v>
       </c>
       <c r="H76" s="3">
-        <v>879400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>880400</v>
+        <v>307900</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J76" s="3">
+        <v>251300</v>
+      </c>
+      <c r="K76" s="3">
         <v>872400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1800</v>
+        <v>82600</v>
       </c>
       <c r="E81" s="3">
-        <v>-20000</v>
+        <v>9500</v>
       </c>
       <c r="F81" s="3">
-        <v>1800</v>
+        <v>13000</v>
       </c>
       <c r="G81" s="3">
-        <v>-7000</v>
+        <v>18400</v>
       </c>
       <c r="H81" s="3">
-        <v>3500</v>
+        <v>15400</v>
       </c>
       <c r="I81" s="3">
-        <v>2300</v>
+        <v>20600</v>
       </c>
       <c r="J81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>5600</v>
       </c>
       <c r="E83" s="3">
-        <v>8400</v>
+        <v>5300</v>
       </c>
       <c r="F83" s="3">
-        <v>8500</v>
+        <v>5300</v>
       </c>
       <c r="G83" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7100</v>
+        <v>9900</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-9300</v>
+        <v>21700</v>
       </c>
       <c r="E89" s="3">
-        <v>-4100</v>
+        <v>17700</v>
       </c>
       <c r="F89" s="3">
-        <v>26100</v>
+        <v>17700</v>
       </c>
       <c r="G89" s="3">
-        <v>23200</v>
+        <v>21400</v>
       </c>
       <c r="H89" s="3">
+        <v>32000</v>
+      </c>
+      <c r="I89" s="3">
         <v>11300</v>
       </c>
-      <c r="I89" s="3">
-        <v>-52900</v>
-      </c>
       <c r="J89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-17600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6200</v>
+        <v>-1700</v>
       </c>
       <c r="E91" s="3">
-        <v>-4800</v>
+        <v>-2100</v>
       </c>
       <c r="F91" s="3">
-        <v>-11600</v>
+        <v>-2100</v>
       </c>
       <c r="G91" s="3">
-        <v>-5400</v>
+        <v>-1100</v>
       </c>
       <c r="H91" s="3">
-        <v>-10200</v>
+        <v>-5500</v>
       </c>
       <c r="I91" s="3">
-        <v>-5400</v>
+        <v>-4400</v>
       </c>
       <c r="J91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-5200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2000</v>
+        <v>153700</v>
       </c>
       <c r="E94" s="3">
-        <v>17500</v>
+        <v>-1700</v>
       </c>
       <c r="F94" s="3">
-        <v>-17100</v>
+        <v>-1700</v>
       </c>
       <c r="G94" s="3">
-        <v>-76800</v>
+        <v>-800</v>
       </c>
       <c r="H94" s="3">
-        <v>-9300</v>
+        <v>-5400</v>
       </c>
       <c r="I94" s="3">
-        <v>23300</v>
+        <v>-13100</v>
       </c>
       <c r="J94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>75000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3335,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-200</v>
+        <v>-85300</v>
       </c>
       <c r="E100" s="3">
-        <v>-300</v>
+        <v>-14500</v>
       </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>-14500</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>-21500</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-25500</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1600</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>-2200</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-13100</v>
+        <v>89500</v>
       </c>
       <c r="E102" s="3">
-        <v>10900</v>
+        <v>1500</v>
       </c>
       <c r="F102" s="3">
-        <v>10300</v>
+        <v>1500</v>
       </c>
       <c r="G102" s="3">
-        <v>-55400</v>
+        <v>-900</v>
       </c>
       <c r="H102" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I102" s="3">
-        <v>-29500</v>
+        <v>-500</v>
       </c>
       <c r="J102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-25500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>250700</v>
+      </c>
+      <c r="E8" s="3">
         <v>151800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>130300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>129100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>133200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>139100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>147600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>141600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>96700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E9" s="3">
         <v>99100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>84300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>81600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>84700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>89200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>96700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>93100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>66600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E10" s="3">
         <v>52700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>49900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,13 +835,14 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
+      <c r="D12" s="3">
+        <v>3700</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
@@ -837,26 +850,29 @@
       <c r="F12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,72 +903,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-72500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
-        <v>1600</v>
-      </c>
       <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>5400</v>
       </c>
       <c r="J15" s="3">
         <v>5400</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E17" s="3">
         <v>144900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>107500</v>
       </c>
-      <c r="G17" s="3">
-        <v>108800</v>
-      </c>
       <c r="H17" s="3">
+        <v>109500</v>
+      </c>
+      <c r="I17" s="3">
         <v>114200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>119400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>116200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E18" s="3">
         <v>6900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21600</v>
       </c>
-      <c r="G18" s="3">
-        <v>24400</v>
-      </c>
       <c r="H18" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I18" s="3">
         <v>24900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1040,168 +1072,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E21" s="3">
         <v>16000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28000</v>
       </c>
-      <c r="G21" s="3">
-        <v>32000</v>
-      </c>
       <c r="H21" s="3">
+        <v>30700</v>
+      </c>
+      <c r="I21" s="3">
         <v>31500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E23" s="3">
         <v>80000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E26" s="3">
         <v>82600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E27" s="3">
         <v>82600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1490,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>1500</v>
-      </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E33" s="3">
         <v>82600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E35" s="3">
         <v>82600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,296 +1702,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E41" s="3">
         <v>99900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="3">
         <v>7400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="3">
         <v>264800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E42" s="3">
         <v>13500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>9500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>32200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E43" s="3">
         <v>250600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>123900</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="3">
         <v>122100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131700</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="3">
         <v>235300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>271200</v>
+      </c>
+      <c r="E44" s="3">
         <v>297500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>146700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3">
         <v>141200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>140200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="3">
         <v>70100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="3">
         <v>71700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>641400</v>
+      </c>
+      <c r="E46" s="3">
         <v>677300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>295000</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="3">
         <v>288300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>295700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="3">
         <v>750000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="3">
         <v>19900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="3">
         <v>20000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E48" s="3">
         <v>229600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="3">
         <v>85100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>84500</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="3">
         <v>186100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>168500</v>
+      </c>
+      <c r="E49" s="3">
         <v>59700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>61700</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>65700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>67700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>23300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2085,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E52" s="3">
         <v>7700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="3">
         <v>10400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2155,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1197500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1132800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>471600</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="3">
         <v>475300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>487000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="3">
         <v>970000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,61 +2222,65 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E57" s="3">
         <v>83600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36700</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="3">
         <v>32000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>39700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="3">
         <v>43000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E58" s="3">
         <v>19800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17200</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>17200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>28100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2157,93 +2290,102 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="3">
         <v>52600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162700</v>
+      </c>
+      <c r="E60" s="3">
         <v>174800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80700</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="3">
         <v>78600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>103100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="3">
         <v>87600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E61" s="3">
         <v>51700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>38400</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>67700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2253,40 +2395,46 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>17</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="3">
         <v>10000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2535,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>239300</v>
+      </c>
+      <c r="E66" s="3">
         <v>228400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119100</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="3">
         <v>146400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>179000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" s="3">
         <v>97600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2725,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>211300</v>
+      </c>
+      <c r="E72" s="3">
         <v>179500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>171900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="3">
         <v>145900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>127500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="3">
         <v>950200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2865,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>958200</v>
+      </c>
+      <c r="E76" s="3">
         <v>904400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>352500</v>
-      </c>
-      <c r="F76" s="3">
-        <v>328900</v>
       </c>
       <c r="G76" s="3">
         <v>328900</v>
       </c>
       <c r="H76" s="3">
+        <v>328900</v>
+      </c>
+      <c r="I76" s="3">
         <v>307900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="3">
         <v>251300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>872400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E81" s="3">
         <v>82600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3027,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
         <v>5600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5300</v>
       </c>
       <c r="F83" s="3">
         <v>5300</v>
       </c>
       <c r="G83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K83" s="3">
-        <v>7100</v>
+      <c r="K83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E89" s="3">
         <v>21700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>17700</v>
       </c>
       <c r="F89" s="3">
         <v>17700</v>
       </c>
       <c r="G89" s="3">
+        <v>17700</v>
+      </c>
+      <c r="H89" s="3">
         <v>21400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>11300</v>
       </c>
       <c r="J89" s="3">
         <v>11300</v>
       </c>
       <c r="K89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="L89" s="3">
         <v>-17600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3287,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-2100</v>
       </c>
       <c r="F91" s="3">
         <v>-2100</v>
       </c>
       <c r="G91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-4400</v>
       </c>
       <c r="J91" s="3">
         <v>-4400</v>
       </c>
       <c r="K91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3390,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="E94" s="3">
         <v>153700</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-1700</v>
       </c>
       <c r="F94" s="3">
         <v>-1700</v>
       </c>
       <c r="G94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-13100</v>
       </c>
       <c r="J94" s="3">
         <v>-13100</v>
       </c>
       <c r="K94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-9600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,17 +3442,18 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>75000</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>17</v>
       </c>
@@ -3236,14 +3469,17 @@
       <c r="J96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,57 +3580,63 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-85300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-14500</v>
       </c>
       <c r="F100" s="3">
         <v>-14500</v>
       </c>
       <c r="G100" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="H100" s="3">
         <v>-21500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1200</v>
       </c>
       <c r="J100" s="3">
         <v>1200</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
-      </c>
-      <c r="E101" s="3">
-        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>17</v>
@@ -3396,42 +3644,48 @@
       <c r="J101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L101" s="3">
         <v>1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E102" s="3">
         <v>89500</v>
-      </c>
-      <c r="E102" s="3">
-        <v>1500</v>
       </c>
       <c r="F102" s="3">
         <v>1500</v>
       </c>
       <c r="G102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1000</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-500</v>
       </c>
       <c r="J102" s="3">
         <v>-500</v>
       </c>
       <c r="K102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L102" s="3">
         <v>-25500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -656,173 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E8" s="3">
         <v>250700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>130300</v>
       </c>
-      <c r="G8" s="3">
-        <v>129100</v>
-      </c>
       <c r="H8" s="3">
+        <v>128000</v>
+      </c>
+      <c r="I8" s="3">
         <v>133200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>147600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>141600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>96700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E9" s="3">
         <v>165800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>99100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>84300</v>
       </c>
-      <c r="G9" s="3">
-        <v>81600</v>
-      </c>
       <c r="H9" s="3">
+        <v>78900</v>
+      </c>
+      <c r="I9" s="3">
         <v>84700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>89200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>96700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>93100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>66600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E10" s="3">
         <v>84900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46000</v>
       </c>
-      <c r="G10" s="3">
-        <v>47500</v>
-      </c>
       <c r="H10" s="3">
+        <v>49100</v>
+      </c>
+      <c r="I10" s="3">
         <v>48500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>49900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,43 +849,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="3">
         <v>3700</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,78 +923,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E14" s="3">
         <v>6500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-72500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7600</v>
       </c>
-      <c r="G14" s="3">
-        <v>4000</v>
-      </c>
       <c r="H14" s="3">
+        <v>600</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E15" s="3">
         <v>12000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6600</v>
       </c>
-      <c r="G15" s="3">
-        <v>5700</v>
-      </c>
       <c r="H15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I15" s="3">
         <v>6100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>5400</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>211200</v>
+      </c>
+      <c r="E17" s="3">
         <v>216100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>144900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>109600</v>
       </c>
-      <c r="G17" s="3">
-        <v>107500</v>
-      </c>
       <c r="H17" s="3">
+        <v>105000</v>
+      </c>
+      <c r="I17" s="3">
         <v>109500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>114200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>119400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>116200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>99200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E18" s="3">
         <v>34600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20700</v>
       </c>
-      <c r="G18" s="3">
-        <v>21600</v>
-      </c>
       <c r="H18" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I18" s="3">
         <v>23700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1073,183 +1106,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-700</v>
-      </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E21" s="3">
         <v>46300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28700</v>
       </c>
-      <c r="G21" s="3">
-        <v>28000</v>
-      </c>
       <c r="H21" s="3">
+        <v>27700</v>
+      </c>
+      <c r="I21" s="3">
         <v>30700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E23" s="3">
         <v>27400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>80000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13900</v>
       </c>
-      <c r="G23" s="3">
-        <v>17700</v>
-      </c>
       <c r="H23" s="3">
+        <v>21500</v>
+      </c>
+      <c r="I23" s="3">
         <v>23500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4300</v>
       </c>
-      <c r="G24" s="3">
-        <v>4700</v>
-      </c>
       <c r="H24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I24" s="3">
         <v>5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E26" s="3">
         <v>31800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>82600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9500</v>
       </c>
-      <c r="G26" s="3">
-        <v>13000</v>
-      </c>
       <c r="H26" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I26" s="3">
         <v>18400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E27" s="3">
         <v>31800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9500</v>
       </c>
-      <c r="G27" s="3">
-        <v>13000</v>
-      </c>
       <c r="H27" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I27" s="3">
         <v>18400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
-        <v>700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E33" s="3">
         <v>31800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>82600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9500</v>
       </c>
-      <c r="G33" s="3">
-        <v>13000</v>
-      </c>
       <c r="H33" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I33" s="3">
         <v>18400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E35" s="3">
         <v>31800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>82600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9500</v>
       </c>
-      <c r="G35" s="3">
-        <v>13000</v>
-      </c>
       <c r="H35" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I35" s="3">
         <v>18400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,323 +1789,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E41" s="3">
         <v>73300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10400</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3">
         <v>7400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="3">
         <v>264800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E42" s="3">
         <v>12300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>9500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>32200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>269100</v>
+      </c>
+      <c r="E43" s="3">
         <v>266300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>250600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>123900</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="3">
         <v>122100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131700</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="3">
         <v>235300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>269300</v>
+      </c>
+      <c r="E44" s="3">
         <v>271200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>297500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>146700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3">
         <v>141200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>140200</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="3">
         <v>70100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="3">
         <v>71700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>632600</v>
+      </c>
+      <c r="E46" s="3">
         <v>641400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>677300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>295000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3">
         <v>288300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>295700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" s="3">
         <v>750000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3">
         <v>19900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19600</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="3">
         <v>20000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>245400</v>
+      </c>
+      <c r="E48" s="3">
         <v>245700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3">
         <v>85100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>84500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="3">
         <v>186100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>180300</v>
+      </c>
+      <c r="E49" s="3">
         <v>168500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>59700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>61700</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>65700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>67700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>23300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" s="3">
         <v>10400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1196000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1197500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1132800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>471600</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="3">
         <v>475300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>487000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="3">
         <v>970000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,67 +2353,71 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E57" s="3">
         <v>65200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>83600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36700</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="3">
         <v>32000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57" s="3">
         <v>43000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E58" s="3">
         <v>21000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17200</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>17200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>28100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2293,102 +2427,111 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E59" s="3">
         <v>18200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6600</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59" s="3">
         <v>52600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E60" s="3">
         <v>162700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>80700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="3">
         <v>78600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>103100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60" s="3">
         <v>87600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E61" s="3">
         <v>70100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>51700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38400</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>67700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>75900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2398,43 +2541,49 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E62" s="3">
         <v>6000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>17</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M62" s="3">
         <v>10000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>217600</v>
+      </c>
+      <c r="E66" s="3">
         <v>239300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>228400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>119100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="3">
         <v>146400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" s="3">
         <v>97600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>225400</v>
+      </c>
+      <c r="E72" s="3">
         <v>211300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>179500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>171900</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="3">
         <v>145900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>127500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" s="3">
         <v>950200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>978400</v>
+      </c>
+      <c r="E76" s="3">
         <v>958200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>904400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>352500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>328900</v>
       </c>
       <c r="H76" s="3">
         <v>328900</v>
       </c>
       <c r="I76" s="3">
+        <v>328900</v>
+      </c>
+      <c r="J76" s="3">
         <v>307900</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="3">
         <v>251300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>872400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E81" s="3">
         <v>31800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>82600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9500</v>
       </c>
-      <c r="G81" s="3">
-        <v>13000</v>
-      </c>
       <c r="H81" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I81" s="3">
         <v>18400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3226,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>5900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>5300</v>
       </c>
       <c r="G83" s="3">
         <v>5300</v>
       </c>
       <c r="H83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I83" s="3">
         <v>9900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L83" s="3">
-        <v>7100</v>
+      <c r="L83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E89" s="3">
         <v>36300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21700</v>
       </c>
-      <c r="F89" s="3">
-        <v>17700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>17700</v>
+      <c r="G89" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H89" s="3">
+        <v>12600</v>
+      </c>
+      <c r="I89" s="3">
         <v>21400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>11300</v>
       </c>
       <c r="K89" s="3">
         <v>11300</v>
       </c>
       <c r="L89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="M89" s="3">
         <v>-17600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-2100</v>
+      <c r="G91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-4400</v>
       </c>
       <c r="K91" s="3">
         <v>-4400</v>
       </c>
       <c r="L91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-5200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>153700</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-1700</v>
+      <c r="G94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-13100</v>
       </c>
       <c r="K94" s="3">
         <v>-13100</v>
       </c>
       <c r="L94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,20 +3676,21 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>75000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>17</v>
       </c>
@@ -3472,14 +3706,17 @@
       <c r="K96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E100" s="3">
         <v>11100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-85300</v>
       </c>
-      <c r="F100" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-14500</v>
+      <c r="G100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H100" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-21500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25500</v>
-      </c>
-      <c r="J100" s="3">
-        <v>1200</v>
       </c>
       <c r="K100" s="3">
         <v>1200</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3627,19 +3876,19 @@
         <v>100</v>
       </c>
       <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>100</v>
       </c>
       <c r="G101" s="3">
         <v>100</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>17</v>
@@ -3647,45 +3896,51 @@
       <c r="K101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M101" s="3">
         <v>1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>89500</v>
       </c>
-      <c r="F102" s="3">
-        <v>1500</v>
-      </c>
       <c r="G102" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-500</v>
       </c>
       <c r="K102" s="3">
         <v>-500</v>
       </c>
       <c r="L102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M102" s="3">
         <v>-25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>224200</v>
+      </c>
+      <c r="E8" s="3">
         <v>240400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>250700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>128000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>133200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>147600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>141600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>96700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E9" s="3">
         <v>163900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>165800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>84300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>78900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>89200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>96700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>93100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>66600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E10" s="3">
         <v>76500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>84900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>46000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>49100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>48500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>51000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3">
         <v>3700</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,84 +943,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
         <v>7400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-72500</v>
       </c>
-      <c r="G14" s="3">
-        <v>7600</v>
-      </c>
       <c r="H14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E15" s="3">
         <v>14900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5400</v>
       </c>
       <c r="L15" s="3">
         <v>5400</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>196300</v>
+      </c>
+      <c r="E17" s="3">
         <v>211200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>216100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>144900</v>
       </c>
-      <c r="G17" s="3">
-        <v>109600</v>
-      </c>
       <c r="H17" s="3">
+        <v>109500</v>
+      </c>
+      <c r="I17" s="3">
         <v>105000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>114200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>119400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>116200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>99200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>29200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6900</v>
       </c>
-      <c r="G18" s="3">
-        <v>20700</v>
-      </c>
       <c r="H18" s="3">
+        <v>20800</v>
+      </c>
+      <c r="I18" s="3">
         <v>23000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1107,198 +1140,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E21" s="3">
         <v>44400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16000</v>
       </c>
-      <c r="G21" s="3">
-        <v>28700</v>
-      </c>
       <c r="H21" s="3">
+        <v>28800</v>
+      </c>
+      <c r="I21" s="3">
         <v>27700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E23" s="3">
         <v>21400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>80000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E24" s="3">
         <v>6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E26" s="3">
         <v>14800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>82600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E27" s="3">
         <v>14800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>82600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E33" s="3">
         <v>14800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>82600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E35" s="3">
         <v>14800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>82600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,236 +1876,255 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E41" s="3">
         <v>68100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10400</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3">
         <v>7400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" s="3">
         <v>264800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E42" s="3">
         <v>10800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>9500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>32200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E43" s="3">
         <v>269100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>266300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>250600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>123900</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="3">
         <v>122100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" s="3">
         <v>235300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>278500</v>
+      </c>
+      <c r="E44" s="3">
         <v>269300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>271200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>297500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>146700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3">
         <v>141200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>140200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" s="3">
         <v>70100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E45" s="3">
         <v>8900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" s="3">
         <v>71700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>670100</v>
+      </c>
+      <c r="E46" s="3">
         <v>632600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>641400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>677300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>295000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="3">
         <v>288300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>295700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" s="3">
         <v>750000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2029,111 +2134,120 @@
       <c r="E47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3">
         <v>19900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3">
         <v>20000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>207200</v>
+      </c>
+      <c r="E48" s="3">
         <v>245400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>245700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="3">
         <v>85100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>84500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" s="3">
         <v>186100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>218900</v>
+      </c>
+      <c r="E49" s="3">
         <v>180300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>168500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>59700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>61700</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>65700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>67700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>23300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>8700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" s="3">
         <v>10400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1227100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1196000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1197500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1132800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>471600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3">
         <v>475300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>487000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" s="3">
         <v>970000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,73 +2484,77 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E57" s="3">
         <v>76400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>83600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36700</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="3">
         <v>32000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" s="3">
         <v>43000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E58" s="3">
         <v>17100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>17200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>28100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2430,111 +2564,120 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E59" s="3">
         <v>15200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" s="3">
         <v>52600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>145700</v>
+      </c>
+      <c r="E60" s="3">
         <v>145800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>162700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>80700</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="3">
         <v>78600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" s="3">
         <v>87600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E61" s="3">
         <v>65600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>70100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>38400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>67700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>75900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2544,46 +2687,52 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>17</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" s="3">
         <v>10000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>231500</v>
+      </c>
+      <c r="E66" s="3">
         <v>217600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>239300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>228400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>119100</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="3">
         <v>146400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>179000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" s="3">
         <v>97600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>232100</v>
+      </c>
+      <c r="E72" s="3">
         <v>225400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>211300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>179500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>171900</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="3">
         <v>145900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>127500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" s="3">
         <v>950200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>995600</v>
+      </c>
+      <c r="E76" s="3">
         <v>978400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>958200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>904400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>352500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>328900</v>
       </c>
       <c r="I76" s="3">
         <v>328900</v>
       </c>
       <c r="J76" s="3">
+        <v>328900</v>
+      </c>
+      <c r="K76" s="3">
         <v>307900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" s="3">
         <v>251300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>872400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E81" s="3">
         <v>14800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>82600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E83" s="3">
         <v>4700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>5300</v>
       </c>
       <c r="H83" s="3">
         <v>5300</v>
       </c>
       <c r="I83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="3">
-        <v>7100</v>
+      <c r="M83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E89" s="3">
         <v>31100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>36300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21700</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H89" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I89" s="3">
         <v>12600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>11300</v>
       </c>
       <c r="L89" s="3">
         <v>11300</v>
       </c>
       <c r="M89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="N89" s="3">
         <v>-17600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-4400</v>
       </c>
       <c r="L91" s="3">
         <v>-4400</v>
       </c>
       <c r="M91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-5200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-72000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>153700</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-13100</v>
       </c>
       <c r="L94" s="3">
         <v>-13100</v>
       </c>
       <c r="M94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,23 +3910,24 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>75000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>17</v>
       </c>
@@ -3709,14 +3943,17 @@
       <c r="L96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,69 +4072,75 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-85300</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H100" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-10300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25500</v>
-      </c>
-      <c r="K100" s="3">
-        <v>1200</v>
       </c>
       <c r="L100" s="3">
         <v>1200</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
         <v>100</v>
       </c>
       <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>100</v>
       </c>
       <c r="H101" s="3">
         <v>100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>17</v>
@@ -3899,48 +4148,54 @@
       <c r="L101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>89500</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1000</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-500</v>
       </c>
       <c r="L102" s="3">
         <v>-500</v>
       </c>
       <c r="M102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N102" s="3">
         <v>-25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-30500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -656,212 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>273600</v>
+      </c>
+      <c r="E8" s="3">
         <v>240000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>224200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>240400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>250700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>151800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>128000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>133200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>147600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>141600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>96700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E9" s="3">
         <v>164100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>152500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>163900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>165800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>78900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>84700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>89200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>96700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>93100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>66600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E10" s="3">
         <v>75900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>71700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>76500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>84900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>49900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>51000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>48500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>30100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,13 +890,14 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
+      <c r="D12" s="3">
+        <v>6700</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
@@ -892,38 +905,41 @@
       <c r="F12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3">
         <v>3700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,96 +982,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-33900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-72500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E15" s="3">
         <v>15400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>5400</v>
       </c>
       <c r="N15" s="3">
         <v>5400</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E17" s="3">
         <v>215000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>196300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>211200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>216100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>105000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>109500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>114200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>119400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>116200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>99200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E18" s="3">
         <v>25000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>34600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1175,96 +1207,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E21" s="3">
         <v>40100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>43000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>30700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1272,131 +1311,140 @@
         <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>58000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>80000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="3">
         <v>18700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E26" s="3">
         <v>39200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>82600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E27" s="3">
         <v>39200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E33" s="3">
         <v>39200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>82600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E35" s="3">
         <v>39200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>82600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,272 +2049,291 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>203400</v>
+      </c>
+      <c r="E41" s="3">
         <v>163400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="3">
         <v>7400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P41" s="3">
         <v>264800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>9500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>32200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E43" s="3">
         <v>251500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>256800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>269100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>266300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>250600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>123900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="3">
         <v>122100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>131700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P43" s="3">
         <v>235300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>248400</v>
+      </c>
+      <c r="E44" s="3">
         <v>275200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>278500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>269300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>271200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>297500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>146700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="3">
         <v>141200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>140200</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P44" s="3">
         <v>70100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E45" s="3">
         <v>5100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P45" s="3">
         <v>71700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E46" s="3">
         <v>710400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>670100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>632600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>641400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>677300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>295000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="3">
         <v>288300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>295700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" s="3">
         <v>750000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2245,123 +2349,132 @@
       <c r="G47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="3">
         <v>19900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="3">
         <v>20000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19400</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E48" s="3">
         <v>213400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>207200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>245400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>245700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>78000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="3">
         <v>85100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>84500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P48" s="3">
         <v>186100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E49" s="3">
         <v>215900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>218900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>180300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>168500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>61700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>65700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>67700</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>23300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2564,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8800</v>
+        <v>10900</v>
       </c>
       <c r="E52" s="3">
         <v>8800</v>
       </c>
       <c r="F52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G52" s="3">
         <v>8700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P52" s="3">
         <v>10400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1268300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1253900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1227100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1196000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1197500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1132800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>471600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="3">
         <v>475300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>487000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P54" s="3">
         <v>970000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,85 +2745,89 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E57" s="3">
         <v>66600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>76400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>65200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>83600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="3">
         <v>32000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P57" s="3">
         <v>43000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E58" s="3">
         <v>19100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17200</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>17200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -2704,129 +2837,138 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E59" s="3">
         <v>17300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P59" s="3">
         <v>52600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E60" s="3">
         <v>148700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>145700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>145800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>162700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="3">
         <v>78600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>103100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P60" s="3">
         <v>87600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E61" s="3">
         <v>63400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>80400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>70100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>38400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>67700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>75900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +2978,58 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>17</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P62" s="3">
         <v>10000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E66" s="3">
         <v>215000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>231500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>217600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>239300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>228400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>119100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" s="3">
         <v>146400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>179000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P66" s="3">
         <v>97600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>285300</v>
+      </c>
+      <c r="E72" s="3">
         <v>271300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>232100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>225400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>211300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>179500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>171900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="3">
         <v>145900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>127500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="3">
         <v>950200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1057700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1039000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>995600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>978400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>958200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>904400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>352500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>328900</v>
       </c>
       <c r="K76" s="3">
         <v>328900</v>
       </c>
       <c r="L76" s="3">
+        <v>328900</v>
+      </c>
+      <c r="M76" s="3">
         <v>307900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O76" s="3">
         <v>251300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>872400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E81" s="3">
         <v>39200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>82600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3822,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E83" s="3">
         <v>7800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5300</v>
       </c>
       <c r="J83" s="3">
         <v>5300</v>
       </c>
       <c r="K83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L83" s="3">
         <v>9900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O83" s="3">
-        <v>7100</v>
+      <c r="O83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E89" s="3">
         <v>48400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>59200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>36300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>11300</v>
       </c>
       <c r="N89" s="3">
         <v>11300</v>
       </c>
       <c r="O89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="P89" s="3">
         <v>-17600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4170,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-4400</v>
       </c>
       <c r="N91" s="3">
         <v>-4400</v>
       </c>
       <c r="O91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="P91" s="3">
         <v>-5200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E94" s="3">
         <v>77600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-72000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>153700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-13100</v>
       </c>
       <c r="N94" s="3">
         <v>-13100</v>
       </c>
       <c r="O94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4159,15 +4392,15 @@
       <c r="F96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>75000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>17</v>
       </c>
@@ -4183,14 +4416,17 @@
       <c r="N96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,81 +4563,87 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-31200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>11100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-85300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25500</v>
-      </c>
-      <c r="M100" s="3">
-        <v>1200</v>
       </c>
       <c r="N100" s="3">
         <v>1200</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>100</v>
       </c>
       <c r="G101" s="3">
         <v>100</v>
       </c>
       <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>17</v>
@@ -4403,54 +4651,60 @@
       <c r="N101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P101" s="3">
         <v>1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E102" s="3">
         <v>94600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>89500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-500</v>
       </c>
       <c r="N102" s="3">
         <v>-500</v>
       </c>
       <c r="O102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P102" s="3">
         <v>-25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>INVX</t>
   </si>
@@ -656,224 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E8" s="3">
         <v>273600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>240000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>224200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>240400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>250700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>151800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>130300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>128000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>133200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>147600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>141600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>96700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>88100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>154500</v>
+      </c>
+      <c r="E9" s="3">
         <v>194500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>164100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>152500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>163900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>165800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>84300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>84700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>89200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>96700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>93100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E10" s="3">
         <v>79100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>76500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>84900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>52700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>49100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>49900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>51000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>48500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>30100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="3">
         <v>6700</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
         <v>3700</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,102 +1002,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E14" s="3">
         <v>5800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-33900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-72500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E15" s="3">
         <v>15500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>5400</v>
       </c>
       <c r="O15" s="3">
         <v>5400</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>210100</v>
+      </c>
+      <c r="E17" s="3">
         <v>242000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>215000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>196300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>211200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>216100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>144900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>109500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>105000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>114200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>119400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>116200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>99200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E18" s="3">
         <v>31600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1208,243 +1241,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E21" s="3">
         <v>48900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>30700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>700</v>
+      <c r="D22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
       </c>
       <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E23" s="3">
         <v>27000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>58000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>80000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>13000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E26" s="3">
         <v>14000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E27" s="3">
         <v>14000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>82600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E33" s="3">
         <v>14000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>82600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E35" s="3">
         <v>14000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>82600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,290 +2136,309 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E41" s="3">
         <v>203400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>163400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>73300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="3">
         <v>7400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q41" s="3">
         <v>264800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>290300</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E42" s="3">
         <v>6000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>9500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>32200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>279800</v>
+      </c>
+      <c r="E43" s="3">
         <v>261000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>251500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>256800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>269100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>266300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>250600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>123900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="3">
         <v>122100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q43" s="3">
         <v>235300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E44" s="3">
         <v>248400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>275200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>278500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>269300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>271200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>297500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>146700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="3">
         <v>141200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>140200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q44" s="3">
         <v>70100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q45" s="3">
         <v>71700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>752900</v>
+      </c>
+      <c r="E46" s="3">
         <v>728000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>710400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>670100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>632600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>641400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>677300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>295000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" s="3">
         <v>288300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>295700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q46" s="3">
         <v>750000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>745800</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2352,129 +2457,138 @@
       <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3">
         <v>19900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="3">
         <v>20000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E48" s="3">
         <v>211100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>213400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>207200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>245400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>245700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>229600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>78000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="3">
         <v>85100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>84500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q48" s="3">
         <v>186100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E49" s="3">
         <v>216000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>215900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>218900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>180300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>168500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>59700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>61700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>65700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>67700</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>23300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2684,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E52" s="3">
         <v>10900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8800</v>
       </c>
       <c r="F52" s="3">
         <v>8800</v>
       </c>
       <c r="G52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="H52" s="3">
         <v>8700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q52" s="3">
         <v>10400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1287700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1268300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1253900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1227100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1196000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1197500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1132800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>471600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="3">
         <v>475300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>487000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q54" s="3">
         <v>970000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>970500</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,91 +2876,95 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E57" s="3">
         <v>60700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>65300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>76400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>65200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>83600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57" s="3">
         <v>32000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q57" s="3">
         <v>43000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E58" s="3">
         <v>19400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>17200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>28100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -2840,138 +2974,147 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E59" s="3">
         <v>19600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q59" s="3">
         <v>52600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E60" s="3">
         <v>148200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>148700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>145700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>145800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>162700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>174800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>80700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60" s="3">
         <v>78600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>103100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q60" s="3">
         <v>87600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>89300</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E61" s="3">
         <v>59900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>63400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>80400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>65600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>70100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>38400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>67700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>75900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2981,55 +3124,61 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>17</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q62" s="3">
         <v>10000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E66" s="3">
         <v>210600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>215000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>231500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>217600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>239300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>228400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>119100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" s="3">
         <v>146400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>179000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q66" s="3">
         <v>97600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>254500</v>
+      </c>
+      <c r="E72" s="3">
         <v>285300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>271300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>232100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>225400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>211300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>179500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>171900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" s="3">
         <v>145900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>127500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q72" s="3">
         <v>950200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>953000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1030900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1057700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1039000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>995600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>978400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>958200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>904400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>352500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>328900</v>
       </c>
       <c r="L76" s="3">
         <v>328900</v>
       </c>
       <c r="M76" s="3">
+        <v>328900</v>
+      </c>
+      <c r="N76" s="3">
         <v>307900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P76" s="3">
         <v>251300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>872400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>864800</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E81" s="3">
         <v>14000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>82600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4021,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E83" s="3">
         <v>12100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5300</v>
       </c>
       <c r="K83" s="3">
         <v>5300</v>
       </c>
       <c r="L83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M83" s="3">
         <v>9900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3">
-        <v>7100</v>
+      <c r="P83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q83" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E89" s="3">
         <v>52200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>48400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>59200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>11300</v>
       </c>
       <c r="O89" s="3">
         <v>11300</v>
       </c>
       <c r="P89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-4400</v>
       </c>
       <c r="O91" s="3">
         <v>-4400</v>
       </c>
       <c r="P91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>77600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>153700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-13100</v>
       </c>
       <c r="O94" s="3">
         <v>-13100</v>
       </c>
       <c r="P94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4395,15 +4629,15 @@
       <c r="G96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>75000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>17</v>
       </c>
@@ -4419,14 +4653,17 @@
       <c r="O96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,87 +4809,93 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-85300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25500</v>
-      </c>
-      <c r="N100" s="3">
-        <v>1200</v>
       </c>
       <c r="O100" s="3">
         <v>1200</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>100</v>
       </c>
       <c r="H101" s="3">
         <v>100</v>
       </c>
       <c r="I101" s="3">
+        <v>100</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>100</v>
       </c>
       <c r="K101" s="3">
         <v>100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>17</v>
@@ -4654,57 +4903,63 @@
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>94600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>89500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-500</v>
       </c>
       <c r="O102" s="3">
         <v>-500</v>
       </c>
       <c r="P102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-30500</v>
       </c>
     </row>
